--- a/task/任务规格转化.xlsx
+++ b/task/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R6a54b4941abb41ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Rb88b89d1b9ed4be0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -410,7 +410,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R989b7ff817654853"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd56c372514a4667"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/task/任务规格转化.xlsx
+++ b/task/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Rb88b89d1b9ed4be0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Rd7b2bf26322c4acf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -316,28 +316,28 @@
         <x:v>输入来源</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>本次客服工单SLA结算业务数据，包含工单库、业务日历、待完成SQL、跨平台启动器和开工说明。</x:v>
+        <x:v>本次客服工单SLA结算使用的工单库、业务日历、待完成SQL、启动器和开工说明。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="108" customHeight="1">
       <x:c r="A6" s="7" t="str">
-        <x:v>输入获取方式</x:v>
+        <x:v>原始输入文件</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>解压输入数据包.zip，阅读README.md，在starter/rebuild_sla.sql完成脚本，再从input_data执行npm run process。</x:v>
+        <x:v>input_data/README.md、input_data/business_calendar.json、input_data/package.json、input_data/starter/rebuild_sla.sql、input_data/support_sla.db、input_data/tools/run-task.mjs</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="108" customHeight="1">
       <x:c r="A7" s="7" t="str">
-        <x:v>原始输入文件</x:v>
+        <x:v>业务目标</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
-        <x:v>input_data/README.md、input_data/business_calendar.json、input_data/package.json、input_data/starter/rebuild_sla.sql、input_data/support_sla.db、input_data/tools/run-task.mjs</x:v>
+        <x:v>把工单处理时长换算为业务日历内的有效分钟，扣除暂停区间，并把超时工单交给对应升级团队。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="108" customHeight="1">
       <x:c r="A8" s="7" t="str">
-        <x:v>目标输出文件</x:v>
+        <x:v>交付物</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
         <x:v>output/support_sla_repaired.db、output/sql/rebuild_sla.sql、output/reports/sla_clock.csv、output/reports/pause_interval_audit.csv、output/reports/breach_queue.csv</x:v>
@@ -345,10 +345,10 @@
     </x:row>
     <x:row r="9" ht="108" customHeight="1">
       <x:c r="A9" s="7" t="str">
-        <x:v>核心操作链</x:v>
+        <x:v>下游用途</x:v>
       </x:c>
       <x:c r="B9" s="7" t="str">
-        <x:v>工单与事件核对→业务日历装载→暂停事件配对→工作分钟轴→测量窗口结算→SLA时钟→超时路由→CSV交付</x:v>
+        <x:v>客服运营复核SLA时钟，班组主管核对暂停区间，升级值班组按队列接单，数据工程人员保留修复库与SQL。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="108" customHeight="1">
@@ -356,7 +356,7 @@
         <x:v>暂停区间结算</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>pause_start和pause_end分别按ticket_id、event_time、event_id编号，再以工单与序号配对；暂停工作分钟只在工单测量窗口内扣减一次。</x:v>
+        <x:v>pause_start和pause_end分别按ticket_id、event_time和event_id编号，再以工单与序号配对；暂停工作分钟只在工单测量窗口内扣减一次。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="108" customHeight="1">
@@ -385,32 +385,32 @@
     </x:row>
     <x:row r="14" ht="108" customHeight="1">
       <x:c r="A14" s="7" t="str">
-        <x:v>完成条件</x:v>
+        <x:v>数据库交接</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
-        <x:v>修复库、完成SQL、SLA时钟、暂停区间审计和升级队列五项交付齐全，数据库与三份CSV中的业务对象彼此闭合。</x:v>
+        <x:v>修复库保留未变的tickets与ticket_events，并提供sla_clock、pause_interval_audit和breach_queue三张派生表。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="108" customHeight="1">
       <x:c r="A15" s="7" t="str">
-        <x:v>可验证点</x:v>
+        <x:v>报告交接</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
-        <x:v>源表、日历合同字段、暂停复合主键、测量终点、有效分钟、阈值、超时状态、升级团队、队列顺序与三份CSV表头。</x:v>
+        <x:v>sla_clock.csv、pause_interval_audit.csv和breach_queue.csv分别使用对应派生表的固定列与业务顺序。</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="108" customHeight="1">
       <x:c r="A16" s="7" t="str">
-        <x:v>不适合作为评分点的内容</x:v>
+        <x:v>实现边界</x:v>
       </x:c>
       <x:c r="B16" s="7" t="str">
-        <x:v>允许调整临时表、CTE、索引名称、SQL排版和标准CSV引号；不得改变输入业务主键、日历边界、固定交付路径或下游字段合同。</x:v>
+        <x:v>临时表、CTE、索引名称、SQL排版和标准CSV引号可自行设计；输入主键、日历边界、交付路径和下游字段保持不变。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd56c372514a4667"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbf3cc2da94540e1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/task/任务规格转化.xlsx
+++ b/task/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Rd7b2bf26322c4acf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R67d0181840ba44f4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table" displayName="Table" ref="A1:B16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table" displayName="Table" ref="A1:B17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="模块"/>
     <x:tableColumn id="2" name="规格内容"/>
@@ -305,23 +305,23 @@
     </x:row>
     <x:row r="4" ht="108" customHeight="1">
       <x:c r="A4" s="7" t="str">
-        <x:v>辅助工具</x:v>
+        <x:v>业务角色</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>Node.js20以上与npm负责准备output、复制只读源库并调用SQLite；PowerShell或系统终端负责启动。</x:v>
+        <x:v>客服运营复核SLA时钟，班组主管核对暂停区间，升级值班组按队列接单，数据工程人员维护结算库和SQL。</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="108" customHeight="1">
       <x:c r="A5" s="7" t="str">
-        <x:v>输入来源</x:v>
+        <x:v>业务输入</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>本次客服工单SLA结算使用的工单库、业务日历、待完成SQL、启动器和开工说明。</x:v>
+        <x:v>本次客服SLA结算输入包含工单库、业务日历、待完成SQL、启动器和README。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="108" customHeight="1">
       <x:c r="A6" s="7" t="str">
-        <x:v>原始输入文件</x:v>
+        <x:v>输入文件</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
         <x:v>input_data/README.md、input_data/business_calendar.json、input_data/package.json、input_data/starter/rebuild_sla.sql、input_data/support_sla.db、input_data/tools/run-task.mjs</x:v>
@@ -329,7 +329,7 @@
     </x:row>
     <x:row r="7" ht="108" customHeight="1">
       <x:c r="A7" s="7" t="str">
-        <x:v>业务目标</x:v>
+        <x:v>结算目标</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
         <x:v>把工单处理时长换算为业务日历内的有效分钟，扣除暂停区间，并把超时工单交给对应升级团队。</x:v>
@@ -337,50 +337,50 @@
     </x:row>
     <x:row r="8" ht="108" customHeight="1">
       <x:c r="A8" s="7" t="str">
-        <x:v>交付物</x:v>
+        <x:v>日历装载</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
-        <x:v>output/support_sla_repaired.db、output/sql/rebuild_sla.sql、output/reports/sla_clock.csv、output/reports/pause_interval_audit.csv、output/reports/breach_queue.csv</x:v>
+        <x:v>SQLite通过readfile和JSON1读取时区、工作日、工作时段、节假日、截止时间、SLA阈值和升级路由。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="108" customHeight="1">
       <x:c r="A9" s="7" t="str">
-        <x:v>下游用途</x:v>
+        <x:v>暂停事件闭合</x:v>
       </x:c>
       <x:c r="B9" s="7" t="str">
-        <x:v>客服运营复核SLA时钟，班组主管核对暂停区间，升级值班组按队列接单，数据工程人员保留修复库与SQL。</x:v>
+        <x:v>pause_start和pause_end分别按ticket_id、event_time和event_id编号，再以工单与序号配对；暂停工作分钟只在工单测量窗口内扣减一次。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="108" customHeight="1">
       <x:c r="A10" s="7" t="str">
-        <x:v>暂停区间结算</x:v>
+        <x:v>工作分钟轴</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>pause_start和pause_end分别按ticket_id、event_time和event_id编号，再以工单与序号配对；暂停工作分钟只在工单测量窗口内扣减一次。</x:v>
+        <x:v>递归CTE按Asia/Shanghai本地整分钟生成时间轴，只保留左闭右开的工作时段，并排除周末和节假日。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="108" customHeight="1">
       <x:c r="A11" s="7" t="str">
-        <x:v>工作日历计时</x:v>
+        <x:v>测量窗口</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
-        <x:v>从business_calendar.json读取时区、工作日、工作时段、节假日和截止时间，以左闭右开的整分钟区间计算有效工作时间。</x:v>
+        <x:v>resolved工单以resolved_at为终点，其他状态使用as_of_local；工单开始前和测量终点后的分钟不参与结算。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="108" customHeight="1">
       <x:c r="A12" s="7" t="str">
-        <x:v>SLA时钟与升级路由</x:v>
+        <x:v>SLA时钟</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
-        <x:v>resolved工单以resolved_at结算，其他状态以as_of_local结算；阈值和升级团队来自业务日历，超时队列按分钟与工单主键排序。</x:v>
+        <x:v>sla_clock按ticket_id记录有效分钟、暂停分钟、优先级阈值、超时分钟和SLA状态。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="108" customHeight="1">
       <x:c r="A13" s="7" t="str">
-        <x:v>SQLite软件步骤</x:v>
+        <x:v>升级队列</x:v>
       </x:c>
       <x:c r="B13" s="7" t="str">
-        <x:v>SQLite通过readfile和JSON1装载日历，用窗口函数闭合暂停事件，用递归CTE建立工作分钟轴，重建三张业务表后由.once写出三份CSV。</x:v>
+        <x:v>breach_queue只接收breached工单，按breach_minutes降序、ticket_id升序排列，并关联升级团队。</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="108" customHeight="1">
@@ -388,29 +388,37 @@
         <x:v>数据库交接</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
-        <x:v>修复库保留未变的tickets与ticket_events，并提供sla_clock、pause_interval_audit和breach_queue三张派生表。</x:v>
+        <x:v>修复库保留未变的tickets与ticket_events，并增加sla_clock、pause_interval_audit和breach_queue三张业务表。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="108" customHeight="1">
       <x:c r="A15" s="7" t="str">
-        <x:v>报告交接</x:v>
+        <x:v>业务报表</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
-        <x:v>sla_clock.csv、pause_interval_audit.csv和breach_queue.csv分别使用对应派生表的固定列与业务顺序。</x:v>
+        <x:v>sla_clock.csv、pause_interval_audit.csv和breach_queue.csv分别交给客服运营、班组主管和升级值班组。</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="108" customHeight="1">
       <x:c r="A16" s="7" t="str">
-        <x:v>实现边界</x:v>
+        <x:v>交付文件</x:v>
       </x:c>
       <x:c r="B16" s="7" t="str">
-        <x:v>临时表、CTE、索引名称、SQL排版和标准CSV引号可自行设计；输入主键、日历边界、交付路径和下游字段保持不变。</x:v>
+        <x:v>output/support_sla_repaired.db、output/sql/rebuild_sla.sql、output/reports/sla_clock.csv、output/reports/pause_interval_audit.csv、output/reports/breach_queue.csv</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="108" customHeight="1">
+      <x:c r="A17" s="7" t="str">
+        <x:v>SQL维护</x:v>
+      </x:c>
+      <x:c r="B17" s="7" t="str">
+        <x:v>临时表、CTE、索引名称和SQL排版可以调整；输入主键、日历边界、队列顺序与交付路径保持一致。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbf3cc2da94540e1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd53ab595028348ab"/>
   </x:tableParts>
 </x:worksheet>
 </file>